--- a/data/PROVICHECK_Base_Datos.xlsx
+++ b/data/PROVICHECK_Base_Datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sectoragro-my.sharepoint.com/personal/dreyes_providenciaco_com/Documents/AAPNLCFA005/provicheck/Provicheck enterprise oficial/PROVICHECK-Enterprise/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{911A2B21-7FFB-4A79-9E62-0BD4743C6A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{911A2B21-7FFB-4A79-9E62-0BD4743C6A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C400B59B-24E4-452C-BCDE-84724007337E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipos" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23206" uniqueCount="1641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23209" uniqueCount="1649">
   <si>
     <t>codigo_equipo</t>
   </si>
@@ -4720,9 +4720,6 @@
   </si>
   <si>
     <t>Diego Perez</t>
-  </si>
-  <si>
-    <t>analista_ccfa</t>
   </si>
   <si>
     <t>Analista</t>
@@ -4971,6 +4968,33 @@
   </si>
   <si>
     <t>Importación de 1236 verificaciones desde 8 archivos Excel</t>
+  </si>
+  <si>
+    <t>dfperez</t>
+  </si>
+  <si>
+    <t>pvasquez</t>
+  </si>
+  <si>
+    <t>avera</t>
+  </si>
+  <si>
+    <t>hdcanaveral</t>
+  </si>
+  <si>
+    <t>lvcordoba</t>
+  </si>
+  <si>
+    <t>jpcruz</t>
+  </si>
+  <si>
+    <t>USR-008</t>
+  </si>
+  <si>
+    <t>Juan Camilo Revelo</t>
+  </si>
+  <si>
+    <t>jcreveloo</t>
   </si>
 </sst>
 </file>
@@ -5255,7 +5279,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="UsuariosTable" displayName="UsuariosTable" ref="A1:I8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="UsuariosTable" displayName="UsuariosTable" ref="A1:I9">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="id_usuario"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="nombre_usuario"/>
@@ -5992,13 +6016,13 @@
   <sheetData>
     <row r="1" spans="1:13" ht="15">
       <c r="A1" s="2" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1607</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>1608</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1609</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
@@ -6007,19 +6031,19 @@
         <v>1</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>1610</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>1611</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>1612</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>1613</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>1614</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>12</v>
@@ -6033,10 +6057,10 @@
     </row>
     <row r="2" spans="1:13" ht="28.5">
       <c r="A2" s="1" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>1615</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1616</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -6046,10 +6070,10 @@
         <v>24</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>1616</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>1617</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>1618</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -6062,10 +6086,10 @@
     </row>
     <row r="3" spans="1:13" ht="28.5">
       <c r="A3" s="1" t="s">
+        <v>1618</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>1619</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1620</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
@@ -6075,10 +6099,10 @@
         <v>24</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -6091,13 +6115,13 @@
     </row>
     <row r="4" spans="1:13" ht="28.5">
       <c r="A4" s="1" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>1615</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>1616</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>40</v>
@@ -6106,10 +6130,10 @@
         <v>41</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -6122,13 +6146,13 @@
     </row>
     <row r="5" spans="1:13" ht="28.5">
       <c r="A5" s="1" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>1623</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>1624</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>1625</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>40</v>
@@ -6137,10 +6161,10 @@
         <v>41</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -6153,10 +6177,10 @@
     </row>
     <row r="6" spans="1:13" ht="28.5">
       <c r="A6" s="1" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
@@ -6166,10 +6190,10 @@
         <v>46</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -6182,13 +6206,13 @@
     </row>
     <row r="7" spans="1:13" ht="28.5">
       <c r="A7" s="1" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>1623</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>1624</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>1625</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>58</v>
@@ -6197,10 +6221,10 @@
         <v>59</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -6232,36 +6256,36 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15">
       <c r="A1" s="2" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1629</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>1630</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1631</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1545</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>1631</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>1632</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>1633</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="28.5">
       <c r="A2" s="1" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>1635</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1636</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1552</v>
@@ -6270,16 +6294,16 @@
         <v>1553</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>1636</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>1637</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>1638</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>1639</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>1640</v>
       </c>
     </row>
   </sheetData>
@@ -96257,7 +96281,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -96333,22 +96357,22 @@
         <v>1558</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1559</v>
+        <v>1640</v>
       </c>
       <c r="D3" s="1">
         <v>80000920</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>1560</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>1561</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>31</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>1556</v>
@@ -96356,28 +96380,28 @@
     </row>
     <row r="4" spans="1:9" ht="28.5">
       <c r="A4" t="s">
+        <v>1562</v>
+      </c>
+      <c r="B4" t="s">
         <v>1563</v>
       </c>
-      <c r="B4" t="s">
-        <v>1564</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>1559</v>
+        <v>1641</v>
       </c>
       <c r="D4">
         <v>80000484</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>1560</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>1561</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>31</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>1556</v>
@@ -96385,28 +96409,28 @@
     </row>
     <row r="5" spans="1:9" ht="28.5">
       <c r="A5" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="B5" t="s">
         <v>1566</v>
       </c>
-      <c r="B5" t="s">
-        <v>1567</v>
-      </c>
       <c r="C5" s="1" t="s">
-        <v>1559</v>
+        <v>1642</v>
       </c>
       <c r="D5">
         <v>809193</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>1560</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>1561</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>31</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>1556</v>
@@ -96414,28 +96438,28 @@
     </row>
     <row r="6" spans="1:9" ht="28.5">
       <c r="A6" s="1" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B6" t="s">
         <v>1569</v>
       </c>
-      <c r="B6" t="s">
-        <v>1570</v>
-      </c>
       <c r="C6" s="1" t="s">
-        <v>1559</v>
+        <v>1643</v>
       </c>
       <c r="D6">
         <v>80001300</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>1560</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>1561</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>31</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>1556</v>
@@ -96443,28 +96467,28 @@
     </row>
     <row r="7" spans="1:9" ht="28.5">
       <c r="A7" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B7" t="s">
         <v>1572</v>
       </c>
-      <c r="B7" t="s">
-        <v>1573</v>
-      </c>
       <c r="C7" s="1" t="s">
-        <v>1559</v>
+        <v>1644</v>
       </c>
       <c r="D7">
         <v>80004786</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>1560</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>1561</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>31</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>1556</v>
@@ -96472,31 +96496,42 @@
     </row>
     <row r="8" spans="1:9" ht="28.5">
       <c r="A8" s="1" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B8" t="s">
         <v>1575</v>
       </c>
-      <c r="B8" t="s">
-        <v>1576</v>
-      </c>
       <c r="C8" s="1" t="s">
-        <v>1559</v>
+        <v>1645</v>
       </c>
       <c r="D8">
         <v>801535</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>1560</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>1561</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>31</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>1556</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>1646</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1647</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1648</v>
       </c>
     </row>
   </sheetData>
@@ -96520,21 +96555,21 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30">
       <c r="A1" s="2" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1578</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>1579</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>1580</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>1581</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>25</v>
@@ -96548,13 +96583,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="B3" t="s">
         <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>31</v>
@@ -96562,13 +96597,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B4" t="s">
         <v>1585</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>1586</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1587</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>31</v>
@@ -96576,13 +96611,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B5" t="s">
         <v>1588</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>1589</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1590</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>31</v>
@@ -96590,13 +96625,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B6" t="s">
         <v>1591</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>1592</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1593</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>31</v>
@@ -96604,13 +96639,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B7" t="s">
         <v>1594</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>1595</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1596</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>31</v>
@@ -96634,15 +96669,15 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15">
       <c r="A1" s="2" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1597</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1598</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>31</v>
@@ -96650,23 +96685,23 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>1599</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1600</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>32</v>
@@ -96674,23 +96709,23 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>1602</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>1603</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>34</v>
@@ -96698,7 +96733,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>87</v>
@@ -96706,7 +96741,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>184</v>
@@ -96714,7 +96749,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>219</v>
@@ -96722,7 +96757,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>517</v>

--- a/data/PROVICHECK_Base_Datos.xlsx
+++ b/data/PROVICHECK_Base_Datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sectoragro-my.sharepoint.com/personal/dreyes_providenciaco_com/Documents/AAPNLCFA005/provicheck/Provicheck enterprise oficial/PROVICHECK-Enterprise/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{911A2B21-7FFB-4A79-9E62-0BD4743C6A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C400B59B-24E4-452C-BCDE-84724007337E}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{911A2B21-7FFB-4A79-9E62-0BD4743C6A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{584C3B0B-8888-4EA4-9DD5-2D93C79BB257}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23209" uniqueCount="1649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23213" uniqueCount="1650">
   <si>
     <t>codigo_equipo</t>
   </si>
@@ -4995,6 +4995,9 @@
   </si>
   <si>
     <t>jcreveloo</t>
+  </si>
+  <si>
+    <t>jcreveloo@provideciaco.com</t>
   </si>
 </sst>
 </file>
@@ -5048,7 +5051,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -5066,6 +5069,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -96533,11 +96539,32 @@
       <c r="C9" t="s">
         <v>1648</v>
       </c>
+      <c r="D9">
+        <v>80005967</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1560</v>
+      </c>
+      <c r="G9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>1649</v>
+      </c>
+      <c r="I9" s="7">
+        <v>46232</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H9" r:id="rId1" xr:uid="{FB36D312-9A6E-4E93-B2CC-01946EB59FB0}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/PROVICHECK_Base_Datos.xlsx
+++ b/data/PROVICHECK_Base_Datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sectoragro-my.sharepoint.com/personal/dreyes_providenciaco_com/Documents/AAPNLCFA005/provicheck/Provicheck enterprise oficial/PROVICHECK-Enterprise/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{911A2B21-7FFB-4A79-9E62-0BD4743C6A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{584C3B0B-8888-4EA4-9DD5-2D93C79BB257}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="8_{911A2B21-7FFB-4A79-9E62-0BD4743C6A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFCB4226-04D1-4B05-B98C-1D5214F13FAC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipos" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23213" uniqueCount="1650">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23220" uniqueCount="1658">
   <si>
     <t>codigo_equipo</t>
   </si>
@@ -4998,6 +4998,30 @@
   </si>
   <si>
     <t>jcreveloo@provideciaco.com</t>
+  </si>
+  <si>
+    <t>PROFESIONAL DE TURNO</t>
+  </si>
+  <si>
+    <t>PRODUCTO TERMINADO II</t>
+  </si>
+  <si>
+    <t>USR-009</t>
+  </si>
+  <si>
+    <t>Carolina Prieto Correal</t>
+  </si>
+  <si>
+    <t>Lider</t>
+  </si>
+  <si>
+    <t>Laboraorio de microbiologia</t>
+  </si>
+  <si>
+    <t>gcprieto@providenciaco.com</t>
+  </si>
+  <si>
+    <t>gcprieto</t>
   </si>
 </sst>
 </file>
@@ -5285,7 +5309,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="UsuariosTable" displayName="UsuariosTable" ref="A1:I9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="UsuariosTable" displayName="UsuariosTable" ref="A1:I10">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="id_usuario"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="nombre_usuario"/>
@@ -5478,7 +5502,7 @@
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="11.5" customWidth="1"/>
+    <col min="4" max="4" width="16.125" customWidth="1"/>
     <col min="5" max="19" width="18" customWidth="1"/>
     <col min="20" max="20" width="15" customWidth="1"/>
     <col min="21" max="22" width="32" customWidth="1"/>
@@ -5567,7 +5591,7 @@
         <v>25</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>25</v>
+        <v>1650</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>26</v>
@@ -5630,7 +5654,7 @@
         <v>25</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>25</v>
+        <v>1651</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>26</v>
@@ -5693,7 +5717,7 @@
         <v>25</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>25</v>
+        <v>1651</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>26</v>
@@ -5819,7 +5843,7 @@
         <v>25</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>25</v>
+        <v>1650</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>26</v>
@@ -5882,7 +5906,7 @@
         <v>25</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>25</v>
+        <v>1651</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>26</v>
@@ -5945,7 +5969,7 @@
         <v>25</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>25</v>
+        <v>1650</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>26</v>
@@ -96287,7 +96311,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -96558,13 +96582,43 @@
         <v>46232</v>
       </c>
     </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1653</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1657</v>
+      </c>
+      <c r="D10">
+        <v>80003967</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1654</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1655</v>
+      </c>
+      <c r="G10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>1656</v>
+      </c>
+      <c r="I10" s="7">
+        <v>46233</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H9" r:id="rId1" xr:uid="{FB36D312-9A6E-4E93-B2CC-01946EB59FB0}"/>
+    <hyperlink ref="H10" r:id="rId2" xr:uid="{477A9A0E-9DF4-4D7B-A8EE-BEAEC35B4ADE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/PROVICHECK_Base_Datos.xlsx
+++ b/data/PROVICHECK_Base_Datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sectoragro-my.sharepoint.com/personal/dreyes_providenciaco_com/Documents/AAPNLCFA005/provicheck/Provicheck enterprise oficial/PROVICHECK-Enterprise/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="8_{911A2B21-7FFB-4A79-9E62-0BD4743C6A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFCB4226-04D1-4B05-B98C-1D5214F13FAC}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="8_{911A2B21-7FFB-4A79-9E62-0BD4743C6A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86A05B68-6DDC-4F26-A07F-C92B9DEB3084}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipos" sheetId="1" r:id="rId1"/>
@@ -5015,13 +5015,13 @@
     <t>Lider</t>
   </si>
   <si>
-    <t>Laboraorio de microbiologia</t>
-  </si>
-  <si>
     <t>gcprieto@providenciaco.com</t>
   </si>
   <si>
     <t>gcprieto</t>
+  </si>
+  <si>
+    <t>Laboratorio de microbiologia</t>
   </si>
 </sst>
 </file>
@@ -5588,7 +5588,7 @@
         <v>24</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>25</v>
+        <v>1560</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>1650</v>
@@ -5651,7 +5651,7 @@
         <v>41</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>25</v>
+        <v>1560</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>1651</v>
@@ -5714,7 +5714,7 @@
         <v>46</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>25</v>
+        <v>1560</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>1651</v>
@@ -5769,7 +5769,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="42.75">
+    <row r="5" spans="1:23" ht="28.5">
       <c r="A5" s="1" t="s">
         <v>51</v>
       </c>
@@ -5777,10 +5777,10 @@
         <v>52</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>53</v>
+        <v>1657</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>53</v>
+        <v>1657</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>26</v>
@@ -5840,7 +5840,7 @@
         <v>59</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>25</v>
+        <v>1560</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>1650</v>
@@ -5903,7 +5903,7 @@
         <v>64</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
+        <v>1560</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>1651</v>
@@ -5966,7 +5966,7 @@
         <v>69</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>25</v>
+        <v>1560</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>1650</v>
@@ -96590,7 +96590,7 @@
         <v>1653</v>
       </c>
       <c r="C10" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="D10">
         <v>80003967</v>
@@ -96599,13 +96599,13 @@
         <v>1654</v>
       </c>
       <c r="F10" t="s">
-        <v>1655</v>
+        <v>1657</v>
       </c>
       <c r="G10" t="s">
         <v>31</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="I10" s="7">
         <v>46233</v>

--- a/data/PROVICHECK_Base_Datos.xlsx
+++ b/data/PROVICHECK_Base_Datos.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="42" documentId="8_{911A2B21-7FFB-4A79-9E62-0BD4743C6A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86A05B68-6DDC-4F26-A07F-C92B9DEB3084}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipos" sheetId="1" r:id="rId1"/>

--- a/data/PROVICHECK_Base_Datos.xlsx
+++ b/data/PROVICHECK_Base_Datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sectoragro-my.sharepoint.com/personal/dreyes_providenciaco_com/Documents/AAPNLCFA005/provicheck/Provicheck enterprise oficial/PROVICHECK-Enterprise/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{911A2B21-7FFB-4A79-9E62-0BD4743C6A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86A05B68-6DDC-4F26-A07F-C92B9DEB3084}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="8_{911A2B21-7FFB-4A79-9E62-0BD4743C6A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F83C91BB-41C6-467E-AD10-C6F95445D20C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="5" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipos" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23220" uniqueCount="1658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23253" uniqueCount="1661">
   <si>
     <t>codigo_equipo</t>
   </si>
@@ -5022,6 +5022,15 @@
   </si>
   <si>
     <t>Laboratorio de microbiologia</t>
+  </si>
+  <si>
+    <t>63065D</t>
+  </si>
+  <si>
+    <t>PV-63065D-20_0</t>
+  </si>
+  <si>
+    <t>Diaria</t>
   </si>
 </sst>
 </file>
@@ -5138,7 +5147,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EquiposTable" displayName="EquiposTable" ref="A1:W8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EquiposTable" displayName="EquiposTable" ref="A1:W9">
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="codigo_equipo"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="nombre_equipo"/>
@@ -5224,7 +5233,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="PuntosVerificacionTable" displayName="PuntosVerificacionTable" ref="A1:N35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="PuntosVerificacionTable" displayName="PuntosVerificacionTable" ref="A1:N36">
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="id_punto"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="codigo_equipo"/>
@@ -5262,7 +5271,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="RelacionEquipoPatronTable" displayName="RelacionEquipoPatronTable" ref="A1:F34">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="RelacionEquipoPatronTable" displayName="RelacionEquipoPatronTable" ref="A1:F35">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="codigo_equipo"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="codigo_patron"/>
@@ -5496,7 +5505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W8"/>
+  <dimension ref="A1:W9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -6019,6 +6028,69 @@
       </c>
       <c r="W8" s="1" t="s">
         <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="30.75" customHeight="1">
+      <c r="A9" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>1560</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>1660</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="W9" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -6490,7 +6562,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="3" width="18" customWidth="1"/>
@@ -8036,6 +8108,50 @@
       </c>
       <c r="N35" s="1" t="s">
         <v>152</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="42.75">
+      <c r="A36" s="1" t="s">
+        <v>1659</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E36" s="1">
+        <v>20</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G36" s="1">
+        <v>19.9998</v>
+      </c>
+      <c r="H36" s="1">
+        <v>20</v>
+      </c>
+      <c r="I36" s="1">
+        <v>20.0002</v>
+      </c>
+      <c r="J36" s="1">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>1660</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -8407,7 +8523,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="5" width="18" customWidth="1"/>
@@ -9091,6 +9207,26 @@
         <v>31</v>
       </c>
       <c r="F34" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="42.75">
+      <c r="A35" s="1" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C35" s="1">
+        <v>20</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>168</v>
       </c>
     </row>

--- a/data/PROVICHECK_Base_Datos.xlsx
+++ b/data/PROVICHECK_Base_Datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sectoragro-my.sharepoint.com/personal/dreyes_providenciaco_com/Documents/AAPNLCFA005/provicheck/Provicheck enterprise oficial/PROVICHECK-Enterprise/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="8_{911A2B21-7FFB-4A79-9E62-0BD4743C6A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F83C91BB-41C6-467E-AD10-C6F95445D20C}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="8_{911A2B21-7FFB-4A79-9E62-0BD4743C6A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F598AECD-C7D0-44DD-9E98-8CE010AA9721}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="5" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipos" sheetId="1" r:id="rId1"/>
@@ -6103,6 +6103,9 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
   <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
@@ -6347,6 +6350,9 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
   <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
@@ -6418,6 +6424,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
   <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
@@ -9240,6 +9249,9 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
   <dimension ref="A1:Y1237"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>

--- a/data/PROVICHECK_Base_Datos.xlsx
+++ b/data/PROVICHECK_Base_Datos.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="57" documentId="8_{911A2B21-7FFB-4A79-9E62-0BD4743C6A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F598AECD-C7D0-44DD-9E98-8CE010AA9721}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipos" sheetId="1" r:id="rId1"/>

--- a/data/PROVICHECK_Base_Datos.xlsx
+++ b/data/PROVICHECK_Base_Datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sectoragro-my.sharepoint.com/personal/dreyes_providenciaco_com/Documents/AAPNLCFA005/provicheck/Provicheck enterprise oficial/PROVICHECK-Enterprise/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="8_{911A2B21-7FFB-4A79-9E62-0BD4743C6A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F598AECD-C7D0-44DD-9E98-8CE010AA9721}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="8_{911A2B21-7FFB-4A79-9E62-0BD4743C6A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{179BE63D-620C-4BDB-B5E0-A89CEFAA9DF9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipos" sheetId="1" r:id="rId1"/>
@@ -8124,7 +8124,7 @@
         <v>1659</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>23</v>
+        <v>1658</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>55</v>

--- a/data/PROVICHECK_Base_Datos.xlsx
+++ b/data/PROVICHECK_Base_Datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sectoragro-my.sharepoint.com/personal/dreyes_providenciaco_com/Documents/AAPNLCFA005/provicheck/Provicheck enterprise oficial/PROVICHECK-Enterprise/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="8_{911A2B21-7FFB-4A79-9E62-0BD4743C6A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{179BE63D-620C-4BDB-B5E0-A89CEFAA9DF9}"/>
+  <xr:revisionPtr revIDLastSave="267" documentId="8_{911A2B21-7FFB-4A79-9E62-0BD4743C6A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0296425-D095-46C2-AE8A-332D2701A6B8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23253" uniqueCount="1661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23408" uniqueCount="1690">
   <si>
     <t>codigo_equipo</t>
   </si>
@@ -5031,6 +5031,93 @@
   </si>
   <si>
     <t>Diaria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POLARIMETRO S&amp;H </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCHMIDT + HAENSCH </t>
+  </si>
+  <si>
+    <t>TOUCH. SACCCHAROMAT 202 W2</t>
+  </si>
+  <si>
+    <t>Polarimetro</t>
+  </si>
+  <si>
+    <t>°Z</t>
+  </si>
+  <si>
+    <t>°A (grados de rotación óptica)</t>
+  </si>
+  <si>
+    <t>63471 Polarimetro S&amp;H</t>
+  </si>
+  <si>
+    <t>AIRE</t>
+  </si>
+  <si>
+    <t>Verificación con cuarzo de referencia (587nm)</t>
+  </si>
+  <si>
+    <t>Verificación aire (587nm)</t>
+  </si>
+  <si>
+    <t>Verificación aire (882nm)</t>
+  </si>
+  <si>
+    <t>PV-AIRE 587-0_0</t>
+  </si>
+  <si>
+    <t>PV-4107 587-25_75</t>
+  </si>
+  <si>
+    <t>PV-4100 587-49_97</t>
+  </si>
+  <si>
+    <t>PV-5383 587-99_91</t>
+  </si>
+  <si>
+    <t>PV-AIRE 882-0_0</t>
+  </si>
+  <si>
+    <t>PV-4107 882-25_80</t>
+  </si>
+  <si>
+    <t>PV-4100 882-50_06</t>
+  </si>
+  <si>
+    <t>PV-5383 882-100_09</t>
+  </si>
+  <si>
+    <t>Verificación con cuarzo de referencia (882nm)</t>
+  </si>
+  <si>
+    <t>AIRE 587</t>
+  </si>
+  <si>
+    <t>4107 587</t>
+  </si>
+  <si>
+    <t>4110 587</t>
+  </si>
+  <si>
+    <t>5383 587</t>
+  </si>
+  <si>
+    <t>AIRE 882</t>
+  </si>
+  <si>
+    <t>4107 882</t>
+  </si>
+  <si>
+    <t>4110 882</t>
+  </si>
+  <si>
+    <t>5383 882</t>
+  </si>
+  <si>
+    <t>4100 882</t>
   </si>
 </sst>
 </file>
@@ -5084,7 +5171,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -5105,12 +5192,31 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -5146,8 +5252,12 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EquiposTable" displayName="EquiposTable" ref="A1:W9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EquiposTable" displayName="EquiposTable" ref="A1:W10">
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="codigo_equipo"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="nombre_equipo"/>
@@ -5233,14 +5343,14 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="PuntosVerificacionTable" displayName="PuntosVerificacionTable" ref="A1:N36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="PuntosVerificacionTable" displayName="PuntosVerificacionTable" ref="A1:N44">
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="id_punto"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="codigo_equipo"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="tipo_equipo"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="nombre_chequeo"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="punto_verificacion"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="unidad"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="unidad" dataDxfId="0"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="limite_inferior_g"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="valor_nominal_g"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="limite_superior_g"/>
@@ -5255,7 +5365,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="EquiposPatronesTable" displayName="EquiposPatronesTable" ref="A1:H13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="EquiposPatronesTable" displayName="EquiposPatronesTable" ref="A1:H21">
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="codigo_patron"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="descripcion"/>
@@ -5271,7 +5381,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="RelacionEquipoPatronTable" displayName="RelacionEquipoPatronTable" ref="A1:F35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="RelacionEquipoPatronTable" displayName="RelacionEquipoPatronTable" ref="A1:F43">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="codigo_equipo"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="codigo_patron"/>
@@ -5505,7 +5615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W9"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -6090,6 +6200,65 @@
         <v>38</v>
       </c>
       <c r="W9" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="28.5" customHeight="1">
+      <c r="A10" s="8">
+        <v>63471</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1661</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>1560</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1662</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>1663</v>
+      </c>
+      <c r="H10" t="s">
+        <v>1664</v>
+      </c>
+      <c r="I10" t="s">
+        <v>1666</v>
+      </c>
+      <c r="J10" t="s">
+        <v>1665</v>
+      </c>
+      <c r="K10" t="s">
+        <v>31</v>
+      </c>
+      <c r="L10" t="s">
+        <v>32</v>
+      </c>
+      <c r="M10" t="s">
+        <v>33</v>
+      </c>
+      <c r="N10" t="s">
+        <v>34</v>
+      </c>
+      <c r="O10" t="s">
+        <v>34</v>
+      </c>
+      <c r="P10" t="s">
+        <v>1660</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>46237</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V10" t="s">
+        <v>1667</v>
+      </c>
+      <c r="W10" s="1" t="s">
         <v>39</v>
       </c>
     </row>
@@ -6571,7 +6740,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="3" width="18" customWidth="1"/>
@@ -6639,7 +6808,7 @@
       <c r="E2" s="1">
         <v>0.02</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G2" s="1">
@@ -6683,7 +6852,7 @@
       <c r="E3" s="1">
         <v>0.05</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G3" s="1">
@@ -6727,7 +6896,7 @@
       <c r="E4" s="1">
         <v>0.1</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G4" s="1">
@@ -6771,7 +6940,7 @@
       <c r="E5" s="1">
         <v>20</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G5" s="1">
@@ -6815,7 +6984,7 @@
       <c r="E6" s="1">
         <v>50</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G6" s="1">
@@ -6859,7 +7028,7 @@
       <c r="E7" s="1">
         <v>100</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G7" s="1">
@@ -6903,7 +7072,7 @@
       <c r="E8" s="1">
         <v>0.02</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G8" s="1">
@@ -6947,7 +7116,7 @@
       <c r="E9" s="1">
         <v>0.05</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G9" s="1">
@@ -6991,7 +7160,7 @@
       <c r="E10" s="1">
         <v>0.1</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G10" s="1">
@@ -7035,7 +7204,7 @@
       <c r="E11" s="1">
         <v>20</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G11" s="1">
@@ -7079,7 +7248,7 @@
       <c r="E12" s="1">
         <v>50</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G12" s="1">
@@ -7123,7 +7292,7 @@
       <c r="E13" s="1">
         <v>100</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G13" s="1">
@@ -7167,7 +7336,7 @@
       <c r="E14" s="1">
         <v>100</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G14" s="1">
@@ -7211,7 +7380,7 @@
       <c r="E15" s="1">
         <v>2</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G15" s="1">
@@ -7255,7 +7424,7 @@
       <c r="E16" s="1">
         <v>10</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G16" s="1">
@@ -7299,7 +7468,7 @@
       <c r="E17" s="1">
         <v>20</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G17" s="1">
@@ -7343,7 +7512,7 @@
       <c r="E18" s="1">
         <v>0.5</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G18" s="1">
@@ -7387,7 +7556,7 @@
       <c r="E19" s="1">
         <v>50</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G19" s="1">
@@ -7431,7 +7600,7 @@
       <c r="E20" s="1">
         <v>100</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G20" s="1">
@@ -7475,7 +7644,7 @@
       <c r="E21" s="1">
         <v>500</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G21" s="1">
@@ -7519,7 +7688,7 @@
       <c r="E22" s="1">
         <v>1000</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G22" s="1">
@@ -7563,7 +7732,7 @@
       <c r="E23" s="1">
         <v>2</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G23" s="1">
@@ -7607,7 +7776,7 @@
       <c r="E24" s="1">
         <v>10</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G24" s="1">
@@ -7651,7 +7820,7 @@
       <c r="E25" s="1">
         <v>20</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G25" s="1">
@@ -7695,7 +7864,7 @@
       <c r="E26" s="1">
         <v>100</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G26" s="1">
@@ -7739,7 +7908,7 @@
       <c r="E27" s="1">
         <v>500</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G27" s="1">
@@ -7783,7 +7952,7 @@
       <c r="E28" s="1">
         <v>1000</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G28" s="1">
@@ -7827,7 +7996,7 @@
       <c r="E29" s="1">
         <v>2000</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G29" s="1">
@@ -7871,7 +8040,7 @@
       <c r="E30" s="1">
         <v>0.5</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G30" s="1">
@@ -7915,7 +8084,7 @@
       <c r="E31" s="1">
         <v>50</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G31" s="1">
@@ -7959,7 +8128,7 @@
       <c r="E32" s="1">
         <v>100</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G32" s="1">
@@ -8003,7 +8172,7 @@
       <c r="E33" s="1">
         <v>500</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G33" s="1">
@@ -8047,7 +8216,7 @@
       <c r="E34" s="1">
         <v>1000</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G34" s="1">
@@ -8091,7 +8260,7 @@
       <c r="E35" s="1">
         <v>0</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G35" s="1">
@@ -8135,7 +8304,7 @@
       <c r="E36" s="1">
         <v>20</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G36" s="1">
@@ -8161,6 +8330,358 @@
       </c>
       <c r="N36" s="1" t="s">
         <v>112</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="25.5" customHeight="1">
+      <c r="A37" s="1" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B37" s="10">
+        <v>63471</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>1670</v>
+      </c>
+      <c r="E37" s="1">
+        <v>0</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>1665</v>
+      </c>
+      <c r="G37" s="1">
+        <v>-0.04</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0</v>
+      </c>
+      <c r="I37" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="J37" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>1660</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N37" s="10" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="24.75" customHeight="1">
+      <c r="A38" s="1" t="s">
+        <v>1673</v>
+      </c>
+      <c r="B38" s="10">
+        <v>63471</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>1669</v>
+      </c>
+      <c r="E38" s="1">
+        <v>25.75</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>1665</v>
+      </c>
+      <c r="G38" s="1">
+        <v>25.71</v>
+      </c>
+      <c r="H38" s="1">
+        <v>25.75</v>
+      </c>
+      <c r="I38" s="1">
+        <v>25.79</v>
+      </c>
+      <c r="J38" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>1660</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N38" s="10">
+        <v>4107</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="24.75" customHeight="1">
+      <c r="A39" s="1" t="s">
+        <v>1674</v>
+      </c>
+      <c r="B39" s="10">
+        <v>63471</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>1669</v>
+      </c>
+      <c r="E39" s="1">
+        <v>49.97</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>1665</v>
+      </c>
+      <c r="G39" s="1">
+        <v>49.93</v>
+      </c>
+      <c r="H39" s="1">
+        <v>49.97</v>
+      </c>
+      <c r="I39" s="1">
+        <v>50.01</v>
+      </c>
+      <c r="J39" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>1660</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N39" s="10">
+        <v>4110</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="23.25" customHeight="1">
+      <c r="A40" s="1" t="s">
+        <v>1675</v>
+      </c>
+      <c r="B40" s="10">
+        <v>63471</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>1669</v>
+      </c>
+      <c r="E40" s="1">
+        <v>99.91</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>1665</v>
+      </c>
+      <c r="G40" s="1">
+        <v>99.87</v>
+      </c>
+      <c r="H40" s="1">
+        <v>99.91</v>
+      </c>
+      <c r="I40" s="1">
+        <v>99.95</v>
+      </c>
+      <c r="J40" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>1660</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N40" s="10">
+        <v>5383</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="42.75">
+      <c r="A41" s="1" t="s">
+        <v>1676</v>
+      </c>
+      <c r="B41" s="10">
+        <v>63471</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>1671</v>
+      </c>
+      <c r="E41" s="1">
+        <v>0</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>1665</v>
+      </c>
+      <c r="G41" s="1">
+        <v>-0.04</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+      <c r="I41" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="J41" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>1660</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N41" s="10" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="42.75">
+      <c r="A42" s="1" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B42" s="10">
+        <v>63471</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>1680</v>
+      </c>
+      <c r="E42" s="12">
+        <v>25.8</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>1665</v>
+      </c>
+      <c r="G42" s="1">
+        <v>25.76</v>
+      </c>
+      <c r="H42" s="12">
+        <v>25.8</v>
+      </c>
+      <c r="I42" s="1">
+        <v>25.84</v>
+      </c>
+      <c r="J42" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>1660</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N42" s="10">
+        <v>4107</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="42.75">
+      <c r="A43" s="1" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B43" s="10">
+        <v>63471</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>1680</v>
+      </c>
+      <c r="E43" s="1">
+        <v>50.06</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>1665</v>
+      </c>
+      <c r="G43" s="1">
+        <v>50.02</v>
+      </c>
+      <c r="H43" s="1">
+        <v>50.06</v>
+      </c>
+      <c r="I43" s="12">
+        <v>50.1</v>
+      </c>
+      <c r="J43" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>1660</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N43" s="10">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="42.75">
+      <c r="A44" s="1" t="s">
+        <v>1679</v>
+      </c>
+      <c r="B44" s="10">
+        <v>63471</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>1680</v>
+      </c>
+      <c r="E44" s="1">
+        <v>100.09</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>1665</v>
+      </c>
+      <c r="G44" s="1">
+        <v>100.04</v>
+      </c>
+      <c r="H44" s="1">
+        <v>100.09</v>
+      </c>
+      <c r="I44" s="1">
+        <v>100.13</v>
+      </c>
+      <c r="J44" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>1660</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N44" s="10">
+        <v>5383</v>
       </c>
     </row>
   </sheetData>
@@ -8173,7 +8694,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -8522,6 +9043,214 @@
         <v>158</v>
       </c>
     </row>
+    <row r="14" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A14" t="s">
+        <v>1681</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1670</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1662</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1665</v>
+      </c>
+      <c r="F14" s="9">
+        <v>46387</v>
+      </c>
+      <c r="G14" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A15" s="8" t="s">
+        <v>1682</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1662</v>
+      </c>
+      <c r="D15">
+        <v>25.75</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1665</v>
+      </c>
+      <c r="F15" s="9">
+        <v>46387</v>
+      </c>
+      <c r="G15" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A16" s="8" t="s">
+        <v>1683</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1662</v>
+      </c>
+      <c r="D16">
+        <v>49.97</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1665</v>
+      </c>
+      <c r="F16" s="9">
+        <v>46387</v>
+      </c>
+      <c r="G16" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A17" s="8" t="s">
+        <v>1684</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1662</v>
+      </c>
+      <c r="D17">
+        <v>99.91</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1665</v>
+      </c>
+      <c r="F17" s="9">
+        <v>46387</v>
+      </c>
+      <c r="G17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="28.5">
+      <c r="A18" t="s">
+        <v>1685</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>1671</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1662</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1665</v>
+      </c>
+      <c r="F18" s="9">
+        <v>46387</v>
+      </c>
+      <c r="G18" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="28.5">
+      <c r="A19" s="8" t="s">
+        <v>1686</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1662</v>
+      </c>
+      <c r="D19">
+        <v>25.8</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1665</v>
+      </c>
+      <c r="F19" s="9">
+        <v>46387</v>
+      </c>
+      <c r="G19" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="28.5">
+      <c r="A20" s="8" t="s">
+        <v>1687</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1662</v>
+      </c>
+      <c r="D20">
+        <v>50.06</v>
+      </c>
+      <c r="E20" t="s">
+        <v>1665</v>
+      </c>
+      <c r="F20" s="9">
+        <v>46387</v>
+      </c>
+      <c r="G20" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="28.5">
+      <c r="A21" s="8" t="s">
+        <v>1688</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1662</v>
+      </c>
+      <c r="D21">
+        <v>100.09</v>
+      </c>
+      <c r="E21" t="s">
+        <v>1665</v>
+      </c>
+      <c r="F21" s="9">
+        <v>46387</v>
+      </c>
+      <c r="G21" t="s">
+        <v>31</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -8532,7 +9261,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="5" width="18" customWidth="1"/>
@@ -9236,6 +9965,166 @@
         <v>31</v>
       </c>
       <c r="F35" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="28.5" customHeight="1">
+      <c r="A36" s="8">
+        <v>63471</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1681</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E36" t="s">
+        <v>31</v>
+      </c>
+      <c r="F36" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="28.5" customHeight="1">
+      <c r="A37" s="8">
+        <v>63471</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>1682</v>
+      </c>
+      <c r="C37">
+        <v>25.75</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F37" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="28.5" customHeight="1">
+      <c r="A38" s="8">
+        <v>63471</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>1683</v>
+      </c>
+      <c r="C38">
+        <v>49.97</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E38" t="s">
+        <v>31</v>
+      </c>
+      <c r="F38" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="28.5" customHeight="1">
+      <c r="A39" s="8">
+        <v>63471</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>1684</v>
+      </c>
+      <c r="C39">
+        <v>99.91</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E39" t="s">
+        <v>31</v>
+      </c>
+      <c r="F39" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="42.75">
+      <c r="A40" s="8">
+        <v>63471</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1685</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E40" t="s">
+        <v>31</v>
+      </c>
+      <c r="F40" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="42.75">
+      <c r="A41" s="8">
+        <v>63471</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>1686</v>
+      </c>
+      <c r="C41" s="13">
+        <v>25.8</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E41" t="s">
+        <v>31</v>
+      </c>
+      <c r="F41" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="42.75">
+      <c r="A42" s="8">
+        <v>63471</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>1689</v>
+      </c>
+      <c r="C42">
+        <v>50.06</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E42" t="s">
+        <v>31</v>
+      </c>
+      <c r="F42" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="42.75">
+      <c r="A43" s="8">
+        <v>63471</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>1688</v>
+      </c>
+      <c r="C43">
+        <v>100.09</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F43" t="s">
         <v>168</v>
       </c>
     </row>
@@ -96443,10 +97332,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U5000">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>U2="No"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>U2="Sí"</formula>
     </cfRule>
   </conditionalFormatting>
